--- a/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskSpecificAssetType001.xlsx
+++ b/tams-invest-parent/tams-invest-risk/src/main/resources/tpl/RskSpecificAssetType001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\code\tams-3.0\tams\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\IdeaProjects\HSbankCode_FlowRisk_2022Version\tams-invest-parent\tams-invest-risk\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DBAF1D-49B6-4DF7-B6C5-56E72BF4ADF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="7590"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>资产代码</t>
   </si>
@@ -43,11 +44,23 @@
     <t>是否信贷资产及其受（收）益权</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>是否无活跃交易市场且需要采用估值技术确定公允价值资产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否不具备活跃交易市场或者在活跃市场中无报价，且不能采用估值技术可靠计量公允价值的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否7个工作日可变现资产</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -404,34 +417,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="31.125" customWidth="1"/>
-    <col min="4" max="4" width="39.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.5" customWidth="1"/>
-    <col min="6" max="6" width="18.75" customWidth="1"/>
+    <col min="3" max="9" width="25.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -442,9 +461,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -453,9 +472,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
